--- a/mock_data.xlsx
+++ b/mock_data.xlsx
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2613</v>
+        <v>1879</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4571</v>
+        <v>8751</v>
       </c>
       <c r="E3" t="n">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2832</v>
+        <v>4262</v>
       </c>
       <c r="E4" t="n">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3086</v>
+        <v>3644</v>
       </c>
       <c r="E5" t="n">
-        <v>180</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2590</v>
+        <v>3756</v>
       </c>
       <c r="E6" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5566</v>
+        <v>4188</v>
       </c>
       <c r="E7" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4642</v>
+        <v>7425</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8766</v>
+        <v>8519</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1288</v>
+        <v>1320</v>
       </c>
       <c r="E10" t="n">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4666</v>
+        <v>5714</v>
       </c>
       <c r="E11" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3649</v>
+        <v>8743</v>
       </c>
       <c r="E12" t="n">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7694</v>
+        <v>5077</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5335</v>
+        <v>9000</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1101</v>
+        <v>5338</v>
       </c>
       <c r="E15" t="n">
-        <v>189</v>
+        <v>70</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8029</v>
+        <v>1218</v>
       </c>
       <c r="E16" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8911</v>
+        <v>7076</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F17" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6583</v>
+        <v>2800</v>
       </c>
       <c r="E18" t="n">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3554</v>
+        <v>6008</v>
       </c>
       <c r="E19" t="n">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8758</v>
+        <v>2061</v>
       </c>
       <c r="E20" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3551</v>
+        <v>6116</v>
       </c>
       <c r="E21" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7124</v>
+        <v>1932</v>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1003</v>
+        <v>4229</v>
       </c>
       <c r="E23" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1596</v>
+        <v>4591</v>
       </c>
       <c r="E24" t="n">
-        <v>193</v>
+        <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6240</v>
+        <v>6314</v>
       </c>
       <c r="E25" t="n">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5843</v>
+        <v>3645</v>
       </c>
       <c r="E26" t="n">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1250</v>
+        <v>8230</v>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1275</v>
+        <v>2315</v>
       </c>
       <c r="E28" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6377</v>
+        <v>5045</v>
       </c>
       <c r="E29" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7805</v>
+        <v>4904</v>
       </c>
       <c r="E30" t="n">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="F30" t="n">
         <v>27</v>
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5193</v>
+        <v>8654</v>
       </c>
       <c r="E31" t="n">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1942</v>
+        <v>1180</v>
       </c>
       <c r="E32" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2000</v>
+        <v>1236</v>
       </c>
       <c r="E33" t="n">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4992</v>
+        <v>1833</v>
       </c>
       <c r="E34" t="n">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
@@ -1268,13 +1268,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1687</v>
+        <v>1282</v>
       </c>
       <c r="E35" t="n">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3151</v>
+        <v>1870</v>
       </c>
       <c r="E36" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3893</v>
+        <v>6963</v>
       </c>
       <c r="E37" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4235</v>
+        <v>7168</v>
       </c>
       <c r="E38" t="n">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="F38" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8693</v>
+        <v>3276</v>
       </c>
       <c r="E39" t="n">
-        <v>56</v>
+        <v>149</v>
       </c>
       <c r="F39" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4046</v>
+        <v>2258</v>
       </c>
       <c r="E40" t="n">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="F40" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41">
@@ -1412,13 +1412,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6370</v>
+        <v>2227</v>
       </c>
       <c r="E41" t="n">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1436,13 +1436,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2887</v>
+        <v>3511</v>
       </c>
       <c r="E42" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F42" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7994</v>
+        <v>6800</v>
       </c>
       <c r="E43" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4609</v>
+        <v>4642</v>
       </c>
       <c r="E44" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8682</v>
+        <v>4706</v>
       </c>
       <c r="E45" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F45" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2270</v>
+        <v>4268</v>
       </c>
       <c r="E46" t="n">
-        <v>151</v>
+        <v>57</v>
       </c>
       <c r="F46" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6802</v>
+        <v>2030</v>
       </c>
       <c r="E47" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F47" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8819</v>
+        <v>7751</v>
       </c>
       <c r="E48" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7024</v>
+        <v>3059</v>
       </c>
       <c r="E49" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1628,13 +1628,13 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7496</v>
+        <v>1357</v>
       </c>
       <c r="E50" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4376</v>
+        <v>3519</v>
       </c>
       <c r="E51" t="n">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="F51" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -1676,13 +1676,13 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1971</v>
+        <v>3442</v>
       </c>
       <c r="E52" t="n">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -1700,13 +1700,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7375</v>
+        <v>8137</v>
       </c>
       <c r="E53" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>8942</v>
+        <v>6341</v>
       </c>
       <c r="E54" t="n">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="F54" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2907</v>
+        <v>4845</v>
       </c>
       <c r="E55" t="n">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2791</v>
+        <v>2186</v>
       </c>
       <c r="E56" t="n">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="F56" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4648</v>
+        <v>2178</v>
       </c>
       <c r="E57" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5493</v>
+        <v>4260</v>
       </c>
       <c r="E58" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F58" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4147</v>
+        <v>5685</v>
       </c>
       <c r="E59" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
@@ -1868,13 +1868,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2411</v>
+        <v>6521</v>
       </c>
       <c r="E60" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6931</v>
+        <v>1005</v>
       </c>
       <c r="E61" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F61" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5339</v>
+        <v>6812</v>
       </c>
       <c r="E62" t="n">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="F62" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63">
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6051</v>
+        <v>8422</v>
       </c>
       <c r="E63" t="n">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F63" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7169</v>
+        <v>2933</v>
       </c>
       <c r="E64" t="n">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2439</v>
+        <v>8063</v>
       </c>
       <c r="E65" t="n">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3902</v>
+        <v>5180</v>
       </c>
       <c r="E66" t="n">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="F66" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
@@ -2036,13 +2036,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8814</v>
+        <v>7793</v>
       </c>
       <c r="E67" t="n">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68">
@@ -2060,13 +2060,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>8381</v>
+        <v>3940</v>
       </c>
       <c r="E68" t="n">
-        <v>200</v>
+        <v>69</v>
       </c>
       <c r="F68" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69">
@@ -2084,13 +2084,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>3107</v>
+        <v>4369</v>
       </c>
       <c r="E69" t="n">
-        <v>179</v>
+        <v>77</v>
       </c>
       <c r="F69" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3243</v>
+        <v>6979</v>
       </c>
       <c r="E70" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="F70" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -2132,13 +2132,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1653</v>
+        <v>1358</v>
       </c>
       <c r="E71" t="n">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="F71" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2139</v>
+        <v>2801</v>
       </c>
       <c r="E72" t="n">
-        <v>160</v>
+        <v>76</v>
       </c>
       <c r="F72" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5792</v>
+        <v>1641</v>
       </c>
       <c r="E73" t="n">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="F73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -2204,13 +2204,13 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>8815</v>
+        <v>3852</v>
       </c>
       <c r="E74" t="n">
-        <v>170</v>
+        <v>123</v>
       </c>
       <c r="F74" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5107</v>
+        <v>1615</v>
       </c>
       <c r="E75" t="n">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6617</v>
+        <v>6901</v>
       </c>
       <c r="E76" t="n">
-        <v>61</v>
+        <v>199</v>
       </c>
       <c r="F76" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1666</v>
+        <v>8765</v>
       </c>
       <c r="E77" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="F77" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>7152</v>
+        <v>8341</v>
       </c>
       <c r="E78" t="n">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="F78" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -2324,13 +2324,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6044</v>
+        <v>3481</v>
       </c>
       <c r="E79" t="n">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="F79" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2936</v>
+        <v>5396</v>
       </c>
       <c r="E80" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6504</v>
+        <v>5247</v>
       </c>
       <c r="E81" t="n">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="F81" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>8942</v>
+        <v>8469</v>
       </c>
       <c r="E82" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83">
@@ -2420,13 +2420,13 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1491</v>
+        <v>7767</v>
       </c>
       <c r="E83" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1936</v>
+        <v>1647</v>
       </c>
       <c r="E84" t="n">
-        <v>97</v>
+        <v>163</v>
       </c>
       <c r="F84" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4819</v>
+        <v>4758</v>
       </c>
       <c r="E85" t="n">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7794</v>
+        <v>5181</v>
       </c>
       <c r="E86" t="n">
-        <v>178</v>
+        <v>94</v>
       </c>
       <c r="F86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -2516,13 +2516,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8649</v>
+        <v>1336</v>
       </c>
       <c r="E87" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="F87" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88">
@@ -2540,13 +2540,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7961</v>
+        <v>4137</v>
       </c>
       <c r="E88" t="n">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="F88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89">
@@ -2564,13 +2564,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>8135</v>
+        <v>3306</v>
       </c>
       <c r="E89" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F89" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8504</v>
+        <v>4346</v>
       </c>
       <c r="E90" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="F90" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -2612,13 +2612,13 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1585</v>
+        <v>3956</v>
       </c>
       <c r="E91" t="n">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="F91" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92">
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1704</v>
+        <v>7282</v>
       </c>
       <c r="E92" t="n">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="F92" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -2660,13 +2660,13 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6505</v>
+        <v>5420</v>
       </c>
       <c r="E93" t="n">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="F93" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94">
@@ -2684,13 +2684,13 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4138</v>
+        <v>6851</v>
       </c>
       <c r="E94" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F94" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7352</v>
+        <v>8606</v>
       </c>
       <c r="E95" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>3422</v>
+        <v>4043</v>
       </c>
       <c r="E96" t="n">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="F96" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97">
@@ -2756,13 +2756,13 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5510</v>
+        <v>3392</v>
       </c>
       <c r="E97" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F97" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98">
@@ -2780,13 +2780,13 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>8667</v>
+        <v>9000</v>
       </c>
       <c r="E98" t="n">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="F98" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1167</v>
+        <v>1177</v>
       </c>
       <c r="E99" t="n">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="F99" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100">
@@ -2828,13 +2828,13 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1479</v>
+        <v>6193</v>
       </c>
       <c r="E100" t="n">
-        <v>188</v>
+        <v>106</v>
       </c>
       <c r="F100" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101">
@@ -2852,13 +2852,13 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3691</v>
+        <v>6408</v>
       </c>
       <c r="E101" t="n">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="F101" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102">
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1172</v>
+        <v>7448</v>
       </c>
       <c r="E102" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="F102" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103">
@@ -2900,13 +2900,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1998</v>
+        <v>4058</v>
       </c>
       <c r="E103" t="n">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="F103" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104">
@@ -2924,13 +2924,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3460</v>
+        <v>1427</v>
       </c>
       <c r="E104" t="n">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="F104" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>4105</v>
+        <v>7245</v>
       </c>
       <c r="E105" t="n">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="F105" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106">
@@ -2972,13 +2972,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>3878</v>
+        <v>5074</v>
       </c>
       <c r="E106" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F106" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -2996,13 +2996,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>7819</v>
+        <v>2135</v>
       </c>
       <c r="E107" t="n">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="F107" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108">
@@ -3020,13 +3020,13 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1242</v>
+        <v>2289</v>
       </c>
       <c r="E108" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="F108" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109">
@@ -3044,13 +3044,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1656</v>
+        <v>4673</v>
       </c>
       <c r="E109" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4778</v>
+        <v>6739</v>
       </c>
       <c r="E110" t="n">
-        <v>69</v>
+        <v>168</v>
       </c>
       <c r="F110" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111">
@@ -3092,13 +3092,13 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7309</v>
+        <v>3014</v>
       </c>
       <c r="E111" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F111" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112">
@@ -3116,13 +3116,13 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5656</v>
+        <v>2710</v>
       </c>
       <c r="E112" t="n">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="F112" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="113">
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2506</v>
+        <v>1601</v>
       </c>
       <c r="E113" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6838</v>
+        <v>4333</v>
       </c>
       <c r="E114" t="n">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115">
@@ -3188,13 +3188,13 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>5086</v>
+        <v>8931</v>
       </c>
       <c r="E115" t="n">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="F115" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116">
@@ -3212,13 +3212,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>8177</v>
+        <v>1237</v>
       </c>
       <c r="E116" t="n">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="F116" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -3236,13 +3236,13 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5747</v>
+        <v>3290</v>
       </c>
       <c r="E117" t="n">
-        <v>166</v>
+        <v>114</v>
       </c>
       <c r="F117" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118">
@@ -3260,13 +3260,13 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2181</v>
+        <v>6070</v>
       </c>
       <c r="E118" t="n">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="F118" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119">
@@ -3284,13 +3284,13 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>5918</v>
+        <v>1676</v>
       </c>
       <c r="E119" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F119" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>6618</v>
+        <v>8718</v>
       </c>
       <c r="E120" t="n">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F120" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121">
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>8699</v>
+        <v>4749</v>
       </c>
       <c r="E121" t="n">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="F121" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3607</v>
+        <v>5905</v>
       </c>
       <c r="E122" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F122" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -3380,13 +3380,13 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1258</v>
+        <v>2004</v>
       </c>
       <c r="E123" t="n">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="F123" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124">
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>3778</v>
+        <v>8575</v>
       </c>
       <c r="E124" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="F124" t="n">
         <v>11</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1404</v>
+        <v>2854</v>
       </c>
       <c r="E125" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F125" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6758</v>
+        <v>2333</v>
       </c>
       <c r="E126" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127">
@@ -3476,13 +3476,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4790</v>
+        <v>6541</v>
       </c>
       <c r="E127" t="n">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="F127" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128">
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5341</v>
+        <v>7957</v>
       </c>
       <c r="E128" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129">
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6656</v>
+        <v>6013</v>
       </c>
       <c r="E129" t="n">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c r="F129" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2026</v>
+        <v>1956</v>
       </c>
       <c r="E130" t="n">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="F130" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131">
@@ -3572,13 +3572,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1156</v>
+        <v>1734</v>
       </c>
       <c r="E131" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F131" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132">
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5162</v>
+        <v>7371</v>
       </c>
       <c r="E132" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F132" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133">
@@ -3620,13 +3620,13 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>8575</v>
+        <v>3105</v>
       </c>
       <c r="E133" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F133" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134">
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2733</v>
+        <v>6185</v>
       </c>
       <c r="E134" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F134" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135">
@@ -3668,13 +3668,13 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2953</v>
+        <v>3020</v>
       </c>
       <c r="E135" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="F135" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="136">
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1998</v>
+        <v>8231</v>
       </c>
       <c r="E136" t="n">
-        <v>192</v>
+        <v>113</v>
       </c>
       <c r="F136" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
@@ -3716,13 +3716,13 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>4311</v>
+        <v>7950</v>
       </c>
       <c r="E137" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138">
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1263</v>
+        <v>2663</v>
       </c>
       <c r="E138" t="n">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="F138" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139">
@@ -3764,13 +3764,13 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7855</v>
+        <v>1343</v>
       </c>
       <c r="E139" t="n">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="F139" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7876</v>
+        <v>2566</v>
       </c>
       <c r="E140" t="n">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="F140" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
@@ -3812,13 +3812,13 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>5160</v>
+        <v>4324</v>
       </c>
       <c r="E141" t="n">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="F141" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
@@ -3836,13 +3836,13 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>4302</v>
+        <v>6969</v>
       </c>
       <c r="E142" t="n">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="F142" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="143">
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6054</v>
+        <v>6473</v>
       </c>
       <c r="E143" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="F143" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="144">
@@ -3884,13 +3884,13 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>8503</v>
+        <v>5178</v>
       </c>
       <c r="E144" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F144" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>8088</v>
+        <v>7730</v>
       </c>
       <c r="E145" t="n">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="F145" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>7350</v>
+        <v>7208</v>
       </c>
       <c r="E146" t="n">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="F146" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="147">
@@ -3956,13 +3956,13 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>8624</v>
+        <v>7452</v>
       </c>
       <c r="E147" t="n">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="F147" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148">
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>5403</v>
+        <v>2622</v>
       </c>
       <c r="E148" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="F148" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149">
@@ -4004,13 +4004,13 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>7364</v>
+        <v>8435</v>
       </c>
       <c r="E149" t="n">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F149" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1935</v>
+        <v>4552</v>
       </c>
       <c r="E150" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="F150" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="151">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4600</v>
+        <v>8139</v>
       </c>
       <c r="E151" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F151" t="n">
         <v>21</v>
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1103</v>
+        <v>8255</v>
       </c>
       <c r="E152" t="n">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="F152" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153">
@@ -4100,13 +4100,13 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1949</v>
+        <v>3322</v>
       </c>
       <c r="E153" t="n">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="F153" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154">
@@ -4124,13 +4124,13 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7061</v>
+        <v>7614</v>
       </c>
       <c r="E154" t="n">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F154" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8163</v>
+        <v>6709</v>
       </c>
       <c r="E155" t="n">
         <v>134</v>
       </c>
       <c r="F155" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156">
@@ -4172,13 +4172,13 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5632</v>
+        <v>3994</v>
       </c>
       <c r="E156" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F156" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>7607</v>
+        <v>4078</v>
       </c>
       <c r="E157" t="n">
-        <v>180</v>
+        <v>88</v>
       </c>
       <c r="F157" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -4220,13 +4220,13 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1231</v>
+        <v>8463</v>
       </c>
       <c r="E158" t="n">
-        <v>192</v>
+        <v>122</v>
       </c>
       <c r="F158" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
@@ -4244,13 +4244,13 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4961</v>
+        <v>4334</v>
       </c>
       <c r="E159" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="F159" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160">
@@ -4268,13 +4268,13 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>8017</v>
+        <v>2406</v>
       </c>
       <c r="E160" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="F160" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161">
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>8225</v>
+        <v>8624</v>
       </c>
       <c r="E161" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="F161" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162">
@@ -4316,13 +4316,13 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>7284</v>
+        <v>2900</v>
       </c>
       <c r="E162" t="n">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="F162" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163">
@@ -4340,13 +4340,13 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>8895</v>
+        <v>4417</v>
       </c>
       <c r="E163" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="F163" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -4364,13 +4364,13 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>7985</v>
+        <v>1692</v>
       </c>
       <c r="E164" t="n">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="F164" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165">
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>6723</v>
+        <v>5770</v>
       </c>
       <c r="E165" t="n">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="F165" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>3497</v>
+        <v>6188</v>
       </c>
       <c r="E166" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="F166" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -4436,13 +4436,13 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>3320</v>
+        <v>4894</v>
       </c>
       <c r="E167" t="n">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="F167" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="168">
@@ -4460,13 +4460,13 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>5972</v>
+        <v>2735</v>
       </c>
       <c r="E168" t="n">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="F168" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="169">
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>6897</v>
+        <v>8175</v>
       </c>
       <c r="E169" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="F169" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170">
@@ -4508,13 +4508,13 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>6517</v>
+        <v>7616</v>
       </c>
       <c r="E170" t="n">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="F170" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171">
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3114</v>
+        <v>1378</v>
       </c>
       <c r="E171" t="n">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="F171" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="172">
@@ -4556,13 +4556,13 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7876</v>
+        <v>5457</v>
       </c>
       <c r="E172" t="n">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="F172" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1321</v>
+        <v>4908</v>
       </c>
       <c r="E173" t="n">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F173" t="n">
         <v>14</v>
@@ -4604,13 +4604,13 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5231</v>
+        <v>6377</v>
       </c>
       <c r="E174" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="F174" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>2011</v>
+        <v>2171</v>
       </c>
       <c r="E175" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F175" t="n">
         <v>21</v>
@@ -4652,13 +4652,13 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>3753</v>
+        <v>8539</v>
       </c>
       <c r="E176" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F176" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177">
@@ -4676,13 +4676,13 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>4891</v>
+        <v>4853</v>
       </c>
       <c r="E177" t="n">
-        <v>192</v>
+        <v>70</v>
       </c>
       <c r="F177" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>6715</v>
+        <v>5274</v>
       </c>
       <c r="E178" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F178" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179">
@@ -4724,13 +4724,13 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1439</v>
+        <v>6073</v>
       </c>
       <c r="E179" t="n">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="F179" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180">
@@ -4748,13 +4748,13 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>4847</v>
+        <v>2753</v>
       </c>
       <c r="E180" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F180" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
@@ -4772,13 +4772,13 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>7586</v>
+        <v>3788</v>
       </c>
       <c r="E181" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="F181" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182">
@@ -4796,13 +4796,13 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1677</v>
+        <v>7051</v>
       </c>
       <c r="E182" t="n">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="F182" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>4493</v>
+        <v>8992</v>
       </c>
       <c r="E183" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="F183" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="184">
@@ -4844,13 +4844,13 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>7712</v>
+        <v>7474</v>
       </c>
       <c r="E184" t="n">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="F184" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="185">
@@ -4868,13 +4868,13 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>3763</v>
+        <v>8231</v>
       </c>
       <c r="E185" t="n">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="F185" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="186">
@@ -4892,13 +4892,13 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>5082</v>
+        <v>8143</v>
       </c>
       <c r="E186" t="n">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="F186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>5844</v>
+        <v>6044</v>
       </c>
       <c r="E187" t="n">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="F187" t="n">
         <v>12</v>
@@ -4940,13 +4940,13 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>4872</v>
+        <v>8632</v>
       </c>
       <c r="E188" t="n">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="F188" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
@@ -4964,13 +4964,13 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3587</v>
+        <v>7182</v>
       </c>
       <c r="E189" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F189" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190">
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>7949</v>
+        <v>2192</v>
       </c>
       <c r="E190" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F190" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191">
@@ -5012,13 +5012,13 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>3032</v>
+        <v>4082</v>
       </c>
       <c r="E191" t="n">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="F191" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>6162</v>
+        <v>8615</v>
       </c>
       <c r="E192" t="n">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F192" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="193">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>5791</v>
+        <v>7108</v>
       </c>
       <c r="E193" t="n">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="F193" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194">
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1848</v>
+        <v>1197</v>
       </c>
       <c r="E194" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F194" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195">
@@ -5108,13 +5108,13 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>7794</v>
+        <v>3741</v>
       </c>
       <c r="E195" t="n">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="F195" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196">
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>4346</v>
+        <v>1084</v>
       </c>
       <c r="E196" t="n">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="F196" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197">
@@ -5156,13 +5156,13 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>6272</v>
+        <v>6570</v>
       </c>
       <c r="E197" t="n">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="F197" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198">
@@ -5180,13 +5180,13 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>4485</v>
+        <v>3115</v>
       </c>
       <c r="E198" t="n">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="F198" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="199">
@@ -5204,13 +5204,13 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>2614</v>
+        <v>4747</v>
       </c>
       <c r="E199" t="n">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="F199" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200">
@@ -5228,13 +5228,13 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>4308</v>
+        <v>5477</v>
       </c>
       <c r="E200" t="n">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="F200" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201">
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>4252</v>
+        <v>8781</v>
       </c>
       <c r="E201" t="n">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="F201" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202">
@@ -5276,13 +5276,13 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1720</v>
+        <v>5582</v>
       </c>
       <c r="E202" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F202" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>7708</v>
+        <v>8206</v>
       </c>
       <c r="E203" t="n">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="F203" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="204">
@@ -5324,13 +5324,13 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>4368</v>
+        <v>8660</v>
       </c>
       <c r="E204" t="n">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="F204" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="205">
@@ -5348,13 +5348,13 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>5245</v>
+        <v>5448</v>
       </c>
       <c r="E205" t="n">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="F205" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="206">
@@ -5372,13 +5372,13 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>3246</v>
+        <v>7057</v>
       </c>
       <c r="E206" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="F206" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207">
@@ -5396,13 +5396,13 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3987</v>
+        <v>3619</v>
       </c>
       <c r="E207" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F207" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208">
@@ -5420,13 +5420,13 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>4240</v>
+        <v>6684</v>
       </c>
       <c r="E208" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F208" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="209">
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>2059</v>
+        <v>5192</v>
       </c>
       <c r="E209" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="F209" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="210">
@@ -5468,13 +5468,13 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>4001</v>
+        <v>2930</v>
       </c>
       <c r="E210" t="n">
-        <v>148</v>
+        <v>54</v>
       </c>
       <c r="F210" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
@@ -5492,13 +5492,13 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>3014</v>
+        <v>8867</v>
       </c>
       <c r="E211" t="n">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="F211" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212">
@@ -5516,13 +5516,13 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>8502</v>
+        <v>1236</v>
       </c>
       <c r="E212" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F212" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213">
@@ -5540,13 +5540,13 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1761</v>
+        <v>6824</v>
       </c>
       <c r="E213" t="n">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="F213" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214">
@@ -5564,13 +5564,13 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>5481</v>
+        <v>6072</v>
       </c>
       <c r="E214" t="n">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="F214" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215">
@@ -5588,13 +5588,13 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>4805</v>
+        <v>7287</v>
       </c>
       <c r="E215" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F215" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="216">
@@ -5612,13 +5612,13 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>3965</v>
+        <v>3940</v>
       </c>
       <c r="E216" t="n">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="F216" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="217">
@@ -5636,13 +5636,13 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>4647</v>
+        <v>4419</v>
       </c>
       <c r="E217" t="n">
-        <v>181</v>
+        <v>126</v>
       </c>
       <c r="F217" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218">
@@ -5660,13 +5660,13 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4059</v>
+        <v>7734</v>
       </c>
       <c r="E218" t="n">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="F218" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="219">
@@ -5684,13 +5684,13 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>2385</v>
+        <v>6754</v>
       </c>
       <c r="E219" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F219" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="220">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>7626</v>
+        <v>4557</v>
       </c>
       <c r="E220" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="F220" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="221">
@@ -5732,13 +5732,13 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>6716</v>
+        <v>7611</v>
       </c>
       <c r="E221" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F221" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="222">
@@ -5756,13 +5756,13 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>8460</v>
+        <v>7390</v>
       </c>
       <c r="E222" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="F222" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="223">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>5363</v>
+        <v>7268</v>
       </c>
       <c r="E223" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="F223" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>8465</v>
+        <v>6782</v>
       </c>
       <c r="E224" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F224" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="225">
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>7491</v>
+        <v>7809</v>
       </c>
       <c r="E225" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="F225" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="226">
@@ -5852,13 +5852,13 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1925</v>
+        <v>3595</v>
       </c>
       <c r="E226" t="n">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="F226" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>6101</v>
+        <v>6623</v>
       </c>
       <c r="E227" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F227" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="228">
@@ -5900,13 +5900,13 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>8103</v>
+        <v>8586</v>
       </c>
       <c r="E228" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F228" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="229">
@@ -5924,13 +5924,13 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>8177</v>
+        <v>3874</v>
       </c>
       <c r="E229" t="n">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="F229" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="230">
@@ -5948,13 +5948,13 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1791</v>
+        <v>7583</v>
       </c>
       <c r="E230" t="n">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="F230" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>7428</v>
+        <v>7827</v>
       </c>
       <c r="E231" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F231" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="232">
@@ -5996,13 +5996,13 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>3404</v>
+        <v>1362</v>
       </c>
       <c r="E232" t="n">
-        <v>61</v>
+        <v>178</v>
       </c>
       <c r="F232" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="233">
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>4938</v>
+        <v>5102</v>
       </c>
       <c r="E233" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="F233" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -6044,13 +6044,13 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>5155</v>
+        <v>8293</v>
       </c>
       <c r="E234" t="n">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="F234" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235">
@@ -6068,13 +6068,13 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>7860</v>
+        <v>7501</v>
       </c>
       <c r="E235" t="n">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="F235" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="236">
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>2188</v>
+        <v>6463</v>
       </c>
       <c r="E236" t="n">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="F236" t="n">
         <v>29</v>
@@ -6116,13 +6116,13 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>7562</v>
+        <v>5978</v>
       </c>
       <c r="E237" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="F237" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238">
@@ -6140,13 +6140,13 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>5465</v>
+        <v>3587</v>
       </c>
       <c r="E238" t="n">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="F238" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -6164,13 +6164,13 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>2009</v>
+        <v>7346</v>
       </c>
       <c r="E239" t="n">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="F239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>5595</v>
+        <v>4600</v>
       </c>
       <c r="E240" t="n">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="F240" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241">
@@ -6212,13 +6212,13 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>3219</v>
+        <v>7383</v>
       </c>
       <c r="E241" t="n">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="F241" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -6236,13 +6236,13 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>4817</v>
+        <v>8236</v>
       </c>
       <c r="E242" t="n">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="F242" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -6260,13 +6260,13 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1794</v>
+        <v>7210</v>
       </c>
       <c r="E243" t="n">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="F243" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244">
@@ -6284,13 +6284,13 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>3599</v>
+        <v>8183</v>
       </c>
       <c r="E244" t="n">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F244" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="245">
@@ -6308,13 +6308,13 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>7428</v>
+        <v>7041</v>
       </c>
       <c r="E245" t="n">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="F245" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="246">
@@ -6332,13 +6332,13 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>8113</v>
+        <v>8749</v>
       </c>
       <c r="E246" t="n">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="F246" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
@@ -6356,13 +6356,13 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>6093</v>
+        <v>1504</v>
       </c>
       <c r="E247" t="n">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="F247" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="248">
@@ -6380,13 +6380,13 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>2738</v>
+        <v>2686</v>
       </c>
       <c r="E248" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F248" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
@@ -6404,13 +6404,13 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>7148</v>
+        <v>1614</v>
       </c>
       <c r="E249" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="F249" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -6428,13 +6428,13 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>2214</v>
+        <v>6082</v>
       </c>
       <c r="E250" t="n">
-        <v>159</v>
+        <v>83</v>
       </c>
       <c r="F250" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251">
@@ -6452,13 +6452,13 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>7833</v>
+        <v>7158</v>
       </c>
       <c r="E251" t="n">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252">
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>5523</v>
+        <v>4011</v>
       </c>
       <c r="E252" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F252" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="253">
@@ -6500,13 +6500,13 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>2226</v>
+        <v>1555</v>
       </c>
       <c r="E253" t="n">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="F253" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254">
@@ -6524,13 +6524,13 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>8523</v>
+        <v>8474</v>
       </c>
       <c r="E254" t="n">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="F254" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>8131</v>
+        <v>8753</v>
       </c>
       <c r="E255" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F255" t="n">
         <v>4</v>
@@ -6572,13 +6572,13 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>7945</v>
+        <v>7427</v>
       </c>
       <c r="E256" t="n">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="F256" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="257">
@@ -6596,13 +6596,13 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>3460</v>
+        <v>5597</v>
       </c>
       <c r="E257" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F257" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="258">
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>6853</v>
+        <v>5479</v>
       </c>
       <c r="E258" t="n">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="F258" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
@@ -6644,13 +6644,13 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>8320</v>
+        <v>5155</v>
       </c>
       <c r="E259" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="F259" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="260">
@@ -6668,13 +6668,13 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1214</v>
+        <v>4815</v>
       </c>
       <c r="E260" t="n">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="F260" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="261">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>2107</v>
+        <v>6266</v>
       </c>
       <c r="E261" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F261" t="n">
         <v>24</v>
@@ -6716,13 +6716,13 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>6395</v>
+        <v>6794</v>
       </c>
       <c r="E262" t="n">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="F262" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="263">
@@ -6740,13 +6740,13 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>8263</v>
+        <v>8394</v>
       </c>
       <c r="E263" t="n">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="F263" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="264">
@@ -6764,13 +6764,13 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>2338</v>
+        <v>3258</v>
       </c>
       <c r="E264" t="n">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="F264" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265">
@@ -6788,13 +6788,13 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>3172</v>
+        <v>4092</v>
       </c>
       <c r="E265" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F265" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="266">
@@ -6812,13 +6812,13 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>6233</v>
+        <v>7831</v>
       </c>
       <c r="E266" t="n">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="F266" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="267">
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>5582</v>
+        <v>3639</v>
       </c>
       <c r="E267" t="n">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="F267" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="268">
@@ -6860,13 +6860,13 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1340</v>
+        <v>3734</v>
       </c>
       <c r="E268" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="F268" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269">
@@ -6884,13 +6884,13 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1852</v>
+        <v>4911</v>
       </c>
       <c r="E269" t="n">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="F269" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="270">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>6732</v>
+        <v>2873</v>
       </c>
       <c r="E270" t="n">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="F270" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="271">
@@ -6932,13 +6932,13 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>6289</v>
+        <v>6247</v>
       </c>
       <c r="E271" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="272">
@@ -6956,13 +6956,13 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2837</v>
+        <v>1892</v>
       </c>
       <c r="E272" t="n">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="F272" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="273">
@@ -6980,13 +6980,13 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>8742</v>
+        <v>6190</v>
       </c>
       <c r="E273" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F273" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="274">
@@ -7004,13 +7004,13 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>4295</v>
+        <v>7843</v>
       </c>
       <c r="E274" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="F274" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="275">
@@ -7028,13 +7028,13 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>4740</v>
+        <v>8731</v>
       </c>
       <c r="E275" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F275" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -7052,13 +7052,13 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1763</v>
+        <v>3490</v>
       </c>
       <c r="E276" t="n">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="F276" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277">
@@ -7076,13 +7076,13 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>5529</v>
+        <v>8118</v>
       </c>
       <c r="E277" t="n">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="F277" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="278">
@@ -7100,13 +7100,13 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>2804</v>
+        <v>5066</v>
       </c>
       <c r="E278" t="n">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="F278" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279">
@@ -7124,13 +7124,13 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>5737</v>
+        <v>6736</v>
       </c>
       <c r="E279" t="n">
-        <v>189</v>
+        <v>59</v>
       </c>
       <c r="F279" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="280">
@@ -7148,13 +7148,13 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>5626</v>
+        <v>4437</v>
       </c>
       <c r="E280" t="n">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="F280" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="281">
@@ -7172,13 +7172,13 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>2502</v>
+        <v>5780</v>
       </c>
       <c r="E281" t="n">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="F281" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="282">
@@ -7196,13 +7196,13 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>5598</v>
+        <v>7524</v>
       </c>
       <c r="E282" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F282" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283">
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>4467</v>
+        <v>3520</v>
       </c>
       <c r="E283" t="n">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="F283" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="284">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>6518</v>
+        <v>7045</v>
       </c>
       <c r="E284" t="n">
-        <v>94</v>
+        <v>157</v>
       </c>
       <c r="F284" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285">
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8413</v>
+        <v>8831</v>
       </c>
       <c r="E285" t="n">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="F285" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="286">
@@ -7292,13 +7292,13 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>5921</v>
+        <v>1342</v>
       </c>
       <c r="E286" t="n">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="F286" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="287">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>4958</v>
+        <v>2746</v>
       </c>
       <c r="E287" t="n">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="F287" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="288">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>8137</v>
+        <v>6532</v>
       </c>
       <c r="E288" t="n">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="F288" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="289">
@@ -7364,13 +7364,13 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1265</v>
+        <v>4076</v>
       </c>
       <c r="E289" t="n">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="F289" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1231</v>
+        <v>908</v>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>257</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
@@ -7443,13 +7443,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1368</v>
+        <v>718</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>159</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>640</v>
+        <v>693</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>778</v>
+        <v>819</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
-        <v>272</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -7500,13 +7500,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1039</v>
+        <v>1497</v>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>172</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
@@ -7519,13 +7519,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1428</v>
+        <v>1461</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
-        <v>178</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8">
@@ -7538,13 +7538,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>626</v>
       </c>
       <c r="D8" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>187</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9">
@@ -7557,13 +7557,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>946</v>
+        <v>973</v>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -7576,13 +7576,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>928</v>
+        <v>857</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>295</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -7595,13 +7595,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>934</v>
+        <v>555</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -7614,13 +7614,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1460</v>
+        <v>735</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>121</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
@@ -7633,13 +7633,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>701</v>
+        <v>1249</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E13" t="n">
-        <v>270</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14">
@@ -7652,13 +7652,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1300</v>
+        <v>954</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E14" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15">
@@ -7671,13 +7671,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>657</v>
+        <v>1231</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
-        <v>291</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16">
@@ -7690,13 +7690,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1167</v>
+        <v>1469</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>267</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17">
@@ -7709,13 +7709,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1029</v>
+        <v>816</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="E17" t="n">
-        <v>216</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18">
@@ -7728,13 +7728,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1149</v>
+        <v>881</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
-        <v>234</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19">
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>605</v>
+        <v>641</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20">
@@ -7766,13 +7766,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1381</v>
+        <v>917</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="E20" t="n">
-        <v>143</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21">
@@ -7785,13 +7785,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1224</v>
+        <v>857</v>
       </c>
       <c r="D21" t="n">
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>157</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22">
@@ -7804,13 +7804,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1233</v>
+        <v>539</v>
       </c>
       <c r="D22" t="n">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
-        <v>247</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>605</v>
+        <v>1451</v>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24">
@@ -7842,13 +7842,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1332</v>
+        <v>1237</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="E24" t="n">
-        <v>208</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25">
@@ -7861,13 +7861,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1179</v>
+        <v>751</v>
       </c>
       <c r="D25" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
-        <v>108</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1318</v>
+        <v>640</v>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>213</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27">
@@ -7899,13 +7899,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>861</v>
+        <v>924</v>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="E27" t="n">
-        <v>171</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>935</v>
+        <v>1273</v>
       </c>
       <c r="D28" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>263</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29">
@@ -7937,13 +7937,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1115</v>
+        <v>1388</v>
       </c>
       <c r="D29" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E29" t="n">
-        <v>245</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30">
@@ -7956,13 +7956,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>725</v>
+        <v>1345</v>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>233</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
@@ -7975,13 +7975,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>510</v>
+        <v>1355</v>
       </c>
       <c r="D31" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E31" t="n">
-        <v>288</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
@@ -7994,13 +7994,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>679</v>
+        <v>1438</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>239</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33">
@@ -8013,13 +8013,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>776</v>
+        <v>1384</v>
       </c>
       <c r="D33" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E33" t="n">
-        <v>240</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34">
@@ -8032,13 +8032,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1295</v>
+        <v>953</v>
       </c>
       <c r="D34" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35">
@@ -8051,13 +8051,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>727</v>
+        <v>774</v>
       </c>
       <c r="D35" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E35" t="n">
-        <v>198</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36">
@@ -8070,13 +8070,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="D36" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E36" t="n">
-        <v>225</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37">
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="D37" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E37" t="n">
-        <v>284</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38">
@@ -8108,13 +8108,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1284</v>
+        <v>1030</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E38" t="n">
-        <v>283</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -8127,13 +8127,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1206</v>
+        <v>915</v>
       </c>
       <c r="D39" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="E39" t="n">
-        <v>130</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40">
@@ -8146,13 +8146,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1037</v>
+        <v>504</v>
       </c>
       <c r="D40" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41">
@@ -8165,13 +8165,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1309</v>
+        <v>1020</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E41" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42">
@@ -8184,13 +8184,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>742</v>
+        <v>1419</v>
       </c>
       <c r="D42" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E42" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43">
@@ -8203,13 +8203,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1048</v>
+        <v>878</v>
       </c>
       <c r="D43" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44">
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>754</v>
+        <v>915</v>
       </c>
       <c r="D44" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E44" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45">
@@ -8241,13 +8241,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>844</v>
+        <v>1155</v>
       </c>
       <c r="D45" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E45" t="n">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46">
@@ -8260,13 +8260,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>992</v>
+        <v>964</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E46" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47">
@@ -8279,13 +8279,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>552</v>
+        <v>708</v>
       </c>
       <c r="D47" t="n">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>108</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48">
@@ -8298,13 +8298,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>518</v>
+        <v>749</v>
       </c>
       <c r="D48" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E48" t="n">
-        <v>271</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49">
@@ -8317,13 +8317,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1444</v>
+        <v>610</v>
       </c>
       <c r="D49" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E49" t="n">
-        <v>162</v>
+        <v>271</v>
       </c>
     </row>
     <row r="50">
@@ -8336,13 +8336,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1184</v>
+        <v>744</v>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E50" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51">
@@ -8355,13 +8355,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>602</v>
+        <v>893</v>
       </c>
       <c r="D51" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E51" t="n">
-        <v>195</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52">
@@ -8374,13 +8374,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>960</v>
+        <v>1304</v>
       </c>
       <c r="D52" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E52" t="n">
-        <v>190</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53">
@@ -8393,13 +8393,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>678</v>
+        <v>566</v>
       </c>
       <c r="D53" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E53" t="n">
-        <v>275</v>
+        <v>254</v>
       </c>
     </row>
     <row r="54">
@@ -8412,13 +8412,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1057</v>
+        <v>565</v>
       </c>
       <c r="D54" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E54" t="n">
-        <v>260</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55">
@@ -8431,13 +8431,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>802</v>
+        <v>1227</v>
       </c>
       <c r="D55" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>246</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56">
@@ -8450,13 +8450,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1135</v>
+        <v>751</v>
       </c>
       <c r="D56" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="E56" t="n">
-        <v>226</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57">
@@ -8469,13 +8469,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>970</v>
+        <v>1169</v>
       </c>
       <c r="D57" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E57" t="n">
-        <v>241</v>
+        <v>276</v>
       </c>
     </row>
     <row r="58">
@@ -8488,13 +8488,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1234</v>
+        <v>1376</v>
       </c>
       <c r="D58" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E58" t="n">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59">
@@ -8507,13 +8507,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>785</v>
+        <v>1288</v>
       </c>
       <c r="D59" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E59" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60">
@@ -8526,13 +8526,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>973</v>
+        <v>1400</v>
       </c>
       <c r="D60" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="E60" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61">
@@ -8545,13 +8545,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1468</v>
+        <v>823</v>
       </c>
       <c r="D61" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E61" t="n">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62">
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>851</v>
+        <v>1036</v>
       </c>
       <c r="D62" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E62" t="n">
-        <v>123</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63">
@@ -8583,13 +8583,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>970</v>
+        <v>1050</v>
       </c>
       <c r="D63" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E63" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64">
@@ -8602,13 +8602,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1453</v>
+        <v>528</v>
       </c>
       <c r="D64" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E64" t="n">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65">
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1207</v>
+        <v>522</v>
       </c>
       <c r="D65" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="E65" t="n">
-        <v>149</v>
+        <v>236</v>
       </c>
     </row>
     <row r="66">
@@ -8640,13 +8640,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1449</v>
+        <v>567</v>
       </c>
       <c r="D66" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E66" t="n">
-        <v>122</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67">
@@ -8659,13 +8659,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>735</v>
+        <v>1053</v>
       </c>
       <c r="D67" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="E67" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68">
@@ -8678,13 +8678,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1174</v>
+        <v>763</v>
       </c>
       <c r="D68" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E68" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69">
@@ -8697,13 +8697,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1131</v>
+        <v>1450</v>
       </c>
       <c r="D69" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="E69" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70">
@@ -8716,13 +8716,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>866</v>
+        <v>1201</v>
       </c>
       <c r="D70" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E70" t="n">
-        <v>256</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71">
@@ -8735,13 +8735,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>881</v>
+        <v>1382</v>
       </c>
       <c r="D71" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E71" t="n">
-        <v>146</v>
+        <v>213</v>
       </c>
     </row>
     <row r="72">
@@ -8754,13 +8754,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1180</v>
+        <v>503</v>
       </c>
       <c r="D72" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E72" t="n">
-        <v>291</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73">
@@ -8773,13 +8773,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>645</v>
+        <v>835</v>
       </c>
       <c r="D73" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E73" t="n">
-        <v>109</v>
+        <v>276</v>
       </c>
     </row>
     <row r="74">
@@ -8792,13 +8792,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>944</v>
+        <v>1257</v>
       </c>
       <c r="D74" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="E74" t="n">
-        <v>215</v>
+        <v>260</v>
       </c>
     </row>
     <row r="75">
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1282</v>
+        <v>578</v>
       </c>
       <c r="D75" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="E75" t="n">
-        <v>211</v>
+        <v>225</v>
       </c>
     </row>
     <row r="76">
@@ -8830,13 +8830,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1314</v>
+        <v>1004</v>
       </c>
       <c r="D76" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="E76" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77">
@@ -8849,13 +8849,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="D77" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="E77" t="n">
-        <v>230</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78">
@@ -8868,13 +8868,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1017</v>
+        <v>933</v>
       </c>
       <c r="D78" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="E78" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79">
@@ -8887,13 +8887,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1232</v>
+        <v>738</v>
       </c>
       <c r="D79" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E79" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80">
@@ -8906,13 +8906,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>902</v>
+        <v>516</v>
       </c>
       <c r="D80" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E80" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1285</v>
+        <v>1439</v>
       </c>
       <c r="D81" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E81" t="n">
-        <v>292</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82">
@@ -8944,13 +8944,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>992</v>
+        <v>875</v>
       </c>
       <c r="D82" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E82" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83">
@@ -8963,13 +8963,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>602</v>
+        <v>1018</v>
       </c>
       <c r="D83" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="E83" t="n">
-        <v>135</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84">
@@ -8982,13 +8982,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1051</v>
+        <v>1339</v>
       </c>
       <c r="D84" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E84" t="n">
-        <v>299</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85">
@@ -9001,13 +9001,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>919</v>
+        <v>606</v>
       </c>
       <c r="D85" t="n">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="E85" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86">
@@ -9020,13 +9020,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>829</v>
+        <v>1037</v>
       </c>
       <c r="D86" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E86" t="n">
-        <v>203</v>
+        <v>285</v>
       </c>
     </row>
     <row r="87">
@@ -9039,13 +9039,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1447</v>
+        <v>1394</v>
       </c>
       <c r="D87" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E87" t="n">
-        <v>147</v>
+        <v>300</v>
       </c>
     </row>
     <row r="88">
@@ -9058,13 +9058,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>905</v>
+        <v>1184</v>
       </c>
       <c r="D88" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E88" t="n">
-        <v>173</v>
+        <v>253</v>
       </c>
     </row>
     <row r="89">
@@ -9077,13 +9077,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>590</v>
+        <v>1146</v>
       </c>
       <c r="D89" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E89" t="n">
-        <v>180</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90">
@@ -9096,13 +9096,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>600</v>
+        <v>924</v>
       </c>
       <c r="D90" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E90" t="n">
-        <v>153</v>
+        <v>104</v>
       </c>
     </row>
     <row r="91">
@@ -9115,13 +9115,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1294</v>
+        <v>980</v>
       </c>
       <c r="D91" t="n">
         <v>95</v>
       </c>
       <c r="E91" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
     </row>
     <row r="92">
@@ -9134,13 +9134,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1218</v>
+        <v>944</v>
       </c>
       <c r="D92" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="E92" t="n">
-        <v>189</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1132</v>
+        <v>586</v>
       </c>
       <c r="D93" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E93" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94">
@@ -9172,13 +9172,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1052</v>
+        <v>1446</v>
       </c>
       <c r="D94" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E94" t="n">
-        <v>272</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95">
@@ -9191,13 +9191,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>740</v>
+        <v>1160</v>
       </c>
       <c r="D95" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E95" t="n">
-        <v>124</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96">
@@ -9210,13 +9210,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1040</v>
+        <v>1251</v>
       </c>
       <c r="D96" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E96" t="n">
-        <v>216</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97">
@@ -9229,13 +9229,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>643</v>
+        <v>1143</v>
       </c>
       <c r="D97" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="E97" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
